--- a/source/Transmittal.Reports.OpenXML/Reports/ProjectDirectory.xlsx
+++ b/source/Transmittal.Reports.OpenXML/Reports/ProjectDirectory.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cb514c15eb25f74/Transmittal Testing/Reports/Style3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{61145117-A026-4C68-8980-049CB51FF30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{271DE3AD-3D86-4B83-AD16-34E816386FCC}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{61145117-A026-4C68-8980-049CB51FF30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31FAA3C4-36D3-4E72-8437-C33186731C28}"/>
   <bookViews>
-    <workbookView xWindow="10080" yWindow="4230" windowWidth="31290" windowHeight="15960" xr2:uid="{8828FE9F-EE50-4BA3-B5C7-ADBF9CA8BE70}"/>
+    <workbookView xWindow="19545" yWindow="5355" windowWidth="28275" windowHeight="19290" xr2:uid="{8828FE9F-EE50-4BA3-B5C7-ADBF9CA8BE70}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Directory" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="ProjectDirectoryData">'Project Directory'!$A$6:$H$6</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>{{ReportTitle}}</t>
   </si>
@@ -59,7 +62,40 @@
     <t>Telephone</t>
   </si>
   <si>
-    <t>Role</t>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>DDI</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>WWW</t>
+  </si>
+  <si>
+    <t>{{Role}}_{{CompanyName}}</t>
+  </si>
+  <si>
+    <t>{{FirstName}} {{LastName}}</t>
+  </si>
+  <si>
+    <t>{{Position}}</t>
+  </si>
+  <si>
+    <t>{{Email}}</t>
+  </si>
+  <si>
+    <t>{{Tel}}</t>
+  </si>
+  <si>
+    <t>{{DDI}}</t>
+  </si>
+  <si>
+    <t>{{Mobile}}</t>
+  </si>
+  <si>
+    <t>{{Website}}</t>
   </si>
 </sst>
 </file>
@@ -111,10 +147,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -131,6 +166,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,47 +489,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26E8EEAE-AAE5-45B7-9879-3E11214BA68A}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="44" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>7</v>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
